--- a/api-hub-example/example.xlsx
+++ b/api-hub-example/example.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/areddy/Downloads/employee-management-service/api-hub-example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A1D81F8-7E95-7646-893A-C4A72854E308}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E98090C7-CE4A-A54D-8F97-173060F0C659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="17880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="API organization (organization)" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="107" uniqueCount="56">
   <si>
     <t>Category</t>
   </si>
@@ -190,12 +190,6 @@
   </si>
   <si>
     <t>dto</t>
-  </si>
-  <si>
-    <t>manager</t>
-  </si>
-  <si>
-    <t>/manager</t>
   </si>
 </sst>
 </file>
@@ -432,12 +426,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="7">
     <cellStyle name="API organization (organization)LockedColumnStyle" xfId="1" xr:uid="{00000000-0005-0000-0000-000006000000}"/>
@@ -797,14 +791,14 @@
       </c>
     </row>
     <row r="2" spans="1:8" ht="17" customHeight="1">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="43" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="38"/>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
       <c r="G2" s="1"/>
       <c r="H2" s="3"/>
     </row>
@@ -1403,15 +1397,9 @@
     </row>
     <row r="28" spans="1:14" ht="15" customHeight="1">
       <c r="A28" s="14"/>
-      <c r="B28" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C28" s="14" t="s">
-        <v>56</v>
-      </c>
-      <c r="D28" s="14" t="s">
-        <v>48</v>
-      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
       <c r="E28" s="16"/>
       <c r="F28" s="16"/>
       <c r="G28" s="16"/>
@@ -1440,45 +1428,31 @@
       <c r="N29" s="15"/>
     </row>
     <row r="30" spans="1:14" ht="15" customHeight="1">
-      <c r="A30" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="B30" s="39"/>
-      <c r="C30" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="D30" s="39"/>
-      <c r="E30" s="40"/>
-      <c r="F30" s="40"/>
-      <c r="G30" s="40"/>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="K30" s="27" t="s">
-        <v>57</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>25</v>
-      </c>
+      <c r="A30" s="40"/>
+      <c r="B30" s="38"/>
+      <c r="C30" s="38"/>
+      <c r="D30" s="38"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="39"/>
+      <c r="G30" s="39"/>
+      <c r="H30" s="39"/>
+      <c r="I30" s="39"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="27"/>
+      <c r="L30" s="12"/>
       <c r="M30" s="8"/>
       <c r="N30" s="8"/>
     </row>
     <row r="31" spans="1:14" ht="15" customHeight="1">
-      <c r="A31" s="42"/>
-      <c r="B31" s="42" t="s">
-        <v>26</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>27</v>
-      </c>
-      <c r="D31" s="42"/>
-      <c r="E31" s="43"/>
-      <c r="F31" s="43"/>
-      <c r="G31" s="43"/>
-      <c r="H31" s="43"/>
-      <c r="I31" s="43"/>
+      <c r="A31" s="41"/>
+      <c r="B31" s="41"/>
+      <c r="C31" s="41"/>
+      <c r="D31" s="41"/>
+      <c r="E31" s="42"/>
+      <c r="F31" s="42"/>
+      <c r="G31" s="42"/>
+      <c r="H31" s="42"/>
+      <c r="I31" s="42"/>
       <c r="J31" s="15"/>
       <c r="K31" s="15"/>
       <c r="L31" s="15"/>
@@ -1487,15 +1461,9 @@
     </row>
     <row r="32" spans="1:14" ht="16" customHeight="1">
       <c r="A32" s="36"/>
-      <c r="B32" s="37" t="s">
-        <v>21</v>
-      </c>
-      <c r="C32" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="D32" s="37" t="s">
-        <v>48</v>
-      </c>
+      <c r="B32" s="37"/>
+      <c r="C32" s="14"/>
+      <c r="D32" s="37"/>
       <c r="E32" s="36"/>
       <c r="F32" s="36"/>
       <c r="G32" s="36"/>
@@ -1504,15 +1472,9 @@
     </row>
     <row r="33" spans="1:9" ht="16" customHeight="1">
       <c r="A33" s="36"/>
-      <c r="B33" s="37" t="s">
-        <v>34</v>
-      </c>
-      <c r="C33" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="D33" s="37" t="s">
-        <v>48</v>
-      </c>
+      <c r="B33" s="37"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="37"/>
       <c r="E33" s="36"/>
       <c r="F33" s="36"/>
       <c r="G33" s="36"/>
@@ -1521,15 +1483,9 @@
     </row>
     <row r="34" spans="1:9" ht="16" customHeight="1">
       <c r="A34" s="36"/>
-      <c r="B34" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C34" s="37" t="s">
-        <v>33</v>
-      </c>
-      <c r="D34" s="37" t="s">
-        <v>48</v>
-      </c>
+      <c r="B34" s="37"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="37"/>
       <c r="E34" s="36"/>
       <c r="F34" s="36"/>
       <c r="G34" s="36"/>
